--- a/registration_forms/032_loyalty_rewards_program_subscription_form--registration_forms.xlsx
+++ b/registration_forms/032_loyalty_rewards_program_subscription_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Business Name</t>
+          <t>Business Name (2)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>contact_number_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Contact Number 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>business_facebook</t>
+          <t>business_facebook_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Business Facebook 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
